--- a/数据对比/指挥数据.xlsx
+++ b/数据对比/指挥数据.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -491,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T128"/>
+  <dimension ref="A1:T136"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="13" style="2" customWidth="1"/>
@@ -554,343 +554,394 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>15</v>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Kassa</t>
+        </is>
       </c>
       <c r="E2" s="3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1">
+        <v>45</v>
+      </c>
+      <c r="G2" s="1">
         <v>28</v>
       </c>
-      <c r="G2" s="1">
-        <v>21</v>
-      </c>
       <c r="H2" s="1">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="I2" s="1">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="J2" s="4">
         <f>(G2+H2)/I2</f>
-        <v>1.7931034482758621</v>
+        <v>1.891304347826087</v>
       </c>
       <c r="K2" s="1">
-        <v>27298</v>
+        <v>24506</v>
       </c>
       <c r="L2" s="1">
-        <v>26752</v>
+        <v>27633</v>
       </c>
       <c r="M2" s="1">
         <f>K2-L2</f>
-        <v>546</v>
+        <v>-3127</v>
       </c>
       <c r="N2" s="5">
         <f>K2/F2</f>
-        <v>974.92857142857144</v>
+        <v>544.5777777777778</v>
       </c>
       <c r="O2" s="6">
-        <v>0.71399999999999997</v>
+        <v>0.622</v>
       </c>
       <c r="P2" s="6">
-        <v>0.25</v>
+        <v>0.536</v>
       </c>
       <c r="Q2" s="7">
-        <v>0</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>CrazyCong</t>
+        </is>
       </c>
       <c r="E3" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="H3" s="1">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="I3" s="1">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J3" s="4">
         <f>(G3+H3)/I3</f>
-        <v>1.6571428571428573</v>
+        <v>2.7142857142857144</v>
       </c>
       <c r="K3" s="1">
-        <v>25270</v>
+        <v>29104</v>
       </c>
       <c r="L3" s="1">
-        <v>22018</v>
+        <v>30007</v>
       </c>
       <c r="M3" s="1">
         <f>K3-L3</f>
-        <v>3252</v>
+        <v>-903</v>
       </c>
       <c r="N3" s="5">
         <f>K3/F3</f>
-        <v>665</v>
+        <v>646.7555555555556</v>
       </c>
       <c r="O3" s="6">
-        <v>0.52600000000000002</v>
+        <v>0.756</v>
       </c>
       <c r="P3" s="6">
-        <v>0.7</v>
+        <v>0.588</v>
       </c>
       <c r="Q3" s="7">
-        <v>0.28599999999999998</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>18</v>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>3mz</t>
+        </is>
+      </c>
+      <c r="E4" s="3">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1">
+        <v>30</v>
+      </c>
+      <c r="I4" s="1">
+        <v>23</v>
+      </c>
+      <c r="J4" s="4">
+        <f>(G4+H4)/I4</f>
+        <v>2.347826086956522</v>
+      </c>
+      <c r="K4" s="1">
+        <v>10891</v>
+      </c>
+      <c r="L4" s="1">
+        <v>13747</v>
+      </c>
+      <c r="M4" s="1">
+        <f>K4-L4</f>
+        <v>-2856</v>
+      </c>
+      <c r="N4" s="5">
+        <f>K4/F4</f>
+        <v>453.7916666666667</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0.361</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0.538</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0.143</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
       </c>
       <c r="E5" s="3">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G5" s="1">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="H5" s="1">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="I5" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="J5" s="4">
         <f>(G5+H5)/I5</f>
-        <v>1.2333333333333334</v>
+        <v>3.0476190476190474</v>
       </c>
       <c r="K5" s="1">
-        <v>16447</v>
+        <v>26335</v>
       </c>
       <c r="L5" s="1">
-        <v>20503</v>
+        <v>26243</v>
       </c>
       <c r="M5" s="1">
         <f>K5-L5</f>
-        <v>-4056</v>
+        <v>92</v>
       </c>
       <c r="N5" s="5">
         <f>K5/F5</f>
-        <v>587.39285714285711</v>
+        <v>585.2222222222222</v>
       </c>
       <c r="O5" s="6">
+        <v>0.467</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0.571</v>
+      </c>
+      <c r="Q5" s="7">
         <v>0.5</v>
-      </c>
-      <c r="P5" s="6">
-        <v>0.28599999999999998</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>18</v>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Bieyun</t>
+        </is>
+      </c>
+      <c r="E6" s="3">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45</v>
+      </c>
+      <c r="G6" s="1">
+        <v>32</v>
+      </c>
+      <c r="H6" s="1">
+        <v>28</v>
+      </c>
+      <c r="I6" s="1">
+        <v>48</v>
+      </c>
+      <c r="J6" s="4">
+        <f>(G6+H6)/I6</f>
+        <v>1.25</v>
+      </c>
+      <c r="K6" s="1">
+        <v>24493</v>
+      </c>
+      <c r="L6" s="1">
+        <v>29260</v>
+      </c>
+      <c r="M6" s="1">
+        <f>K6-L6</f>
+        <v>-4767</v>
+      </c>
+      <c r="N6" s="5">
+        <f>K6/F6</f>
+        <v>544.2888888888889</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0.644</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0.414</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0.083</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>18</v>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E7" s="3">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1">
+        <v>41</v>
+      </c>
+      <c r="J7" s="4">
+        <f>(G7+H7)/I7</f>
+        <v>1.0975609756097562</v>
+      </c>
+      <c r="K7" s="1">
+        <v>14326</v>
+      </c>
+      <c r="L7" s="1">
+        <v>15659</v>
+      </c>
+      <c r="M7" s="1">
+        <f>K7-L7</f>
+        <v>-1333</v>
+      </c>
+      <c r="N7" s="5">
+        <f>K7/F7</f>
+        <v>397.94444444444446</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0.333</v>
+      </c>
+      <c r="P7" s="6">
+        <v>0.417</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>18</v>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Mingyue</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -944,7 +995,7 @@
     </row>
     <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -952,46 +1003,46 @@
         <v>16</v>
       </c>
       <c r="E10" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H10" s="1">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="I10" s="1">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J10" s="4">
         <f>(G10+H10)/I10</f>
-        <v>2.3181818181818183</v>
+        <v>1.7931034482758621</v>
       </c>
       <c r="K10" s="1">
-        <v>38044</v>
+        <v>27298</v>
       </c>
       <c r="L10" s="1">
-        <v>33907</v>
+        <v>26752</v>
       </c>
       <c r="M10" s="1">
         <f>K10-L10</f>
-        <v>4137</v>
+        <v>546</v>
       </c>
       <c r="N10" s="5">
         <f>K10/F10</f>
-        <v>864.63636363636363</v>
+        <v>974.92857142857144</v>
       </c>
       <c r="O10" s="6">
-        <v>0.61399999999999999</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="P10" s="6">
-        <v>0.77800000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="Q10" s="7">
-        <v>9.5000000000000001E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1002,46 +1053,46 @@
         <v>17</v>
       </c>
       <c r="E11" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="H11" s="1">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="I11" s="1">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J11" s="4">
         <f>(G11+H11)/I11</f>
-        <v>2.86046511627907</v>
+        <v>1.6571428571428573</v>
       </c>
       <c r="K11" s="1">
-        <v>32785</v>
+        <v>25270</v>
       </c>
       <c r="L11" s="1">
-        <v>24372</v>
+        <v>22018</v>
       </c>
       <c r="M11" s="1">
         <f>K11-L11</f>
-        <v>8413</v>
+        <v>3252</v>
       </c>
       <c r="N11" s="5">
         <f>K11/F11</f>
-        <v>745.11363636363637</v>
+        <v>665</v>
       </c>
       <c r="O11" s="6">
-        <v>0.65900000000000003</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="P11" s="6">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="Q11" s="7">
-        <v>0.2</v>
+        <v>0.28599999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1051,47 +1102,44 @@
       <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="3">
-        <v>23</v>
-      </c>
-      <c r="F12" s="1">
-        <v>36</v>
-      </c>
-      <c r="G12" s="1">
-        <v>25</v>
-      </c>
-      <c r="H12" s="1">
-        <v>31</v>
-      </c>
-      <c r="I12" s="1">
-        <v>37</v>
-      </c>
-      <c r="J12" s="4">
-        <f>(G12+H12)/I12</f>
-        <v>1.5135135135135136</v>
-      </c>
-      <c r="K12" s="1">
-        <v>20473</v>
-      </c>
-      <c r="L12" s="1">
-        <v>23721</v>
-      </c>
-      <c r="M12" s="1">
-        <f>K12-L12</f>
-        <v>-3248</v>
-      </c>
-      <c r="N12" s="5">
-        <f>K12/F12</f>
-        <v>568.69444444444446</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0.47199999999999998</v>
-      </c>
-      <c r="P12" s="6">
-        <v>0.35299999999999998</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
+      <c r="E12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1102,43 +1150,43 @@
         <v>20</v>
       </c>
       <c r="E13" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H13" s="1">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="I13" s="1">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J13" s="4">
         <f>(G13+H13)/I13</f>
-        <v>2.4318181818181817</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="K13" s="1">
-        <v>28624</v>
+        <v>16447</v>
       </c>
       <c r="L13" s="1">
-        <v>26622</v>
+        <v>20503</v>
       </c>
       <c r="M13" s="1">
         <f>K13-L13</f>
-        <v>2002</v>
+        <v>-4056</v>
       </c>
       <c r="N13" s="5">
         <f>K13/F13</f>
-        <v>650.5454545454545</v>
+        <v>587.39285714285711</v>
       </c>
       <c r="O13" s="6">
-        <v>0.61399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="P13" s="6">
-        <v>0.59299999999999997</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="Q13" s="7">
         <v>0.25</v>
@@ -1151,47 +1199,44 @@
       <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="3">
-        <v>14</v>
-      </c>
-      <c r="F14" s="1">
-        <v>44</v>
-      </c>
-      <c r="G14" s="1">
-        <v>32</v>
-      </c>
-      <c r="H14" s="1">
-        <v>50</v>
-      </c>
-      <c r="I14" s="1">
-        <v>46</v>
-      </c>
-      <c r="J14" s="4">
-        <f>(G14+H14)/I14</f>
-        <v>1.7826086956521738</v>
-      </c>
-      <c r="K14" s="1">
-        <v>25908</v>
-      </c>
-      <c r="L14" s="1">
-        <v>34120</v>
-      </c>
-      <c r="M14" s="1">
-        <f>K14-L14</f>
-        <v>-8212</v>
-      </c>
-      <c r="N14" s="5">
-        <f>K14/F14</f>
-        <v>588.81818181818187</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="P14" s="6">
-        <v>0.32100000000000001</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0.222</v>
+      <c r="E14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1339,7 +1384,7 @@
     </row>
     <row r="18" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1347,46 +1392,46 @@
         <v>16</v>
       </c>
       <c r="E18" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G18" s="1">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H18" s="1">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="I18" s="1">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J18" s="4">
         <f>(G18+H18)/I18</f>
-        <v>1.0857142857142856</v>
+        <v>2.3181818181818183</v>
       </c>
       <c r="K18" s="1">
-        <v>15917</v>
+        <v>38044</v>
       </c>
       <c r="L18" s="1">
-        <v>19533</v>
+        <v>33907</v>
       </c>
       <c r="M18" s="1">
         <f>K18-L18</f>
-        <v>-3616</v>
+        <v>4137</v>
       </c>
       <c r="N18" s="5">
         <f>K18/F18</f>
-        <v>530.56666666666672</v>
+        <v>864.63636363636363</v>
       </c>
       <c r="O18" s="6">
-        <v>0.433</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="P18" s="6">
-        <v>0.38500000000000001</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="Q18" s="7">
-        <v>0</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1397,46 +1442,46 @@
         <v>17</v>
       </c>
       <c r="E19" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G19" s="1">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="H19" s="1">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="I19" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="J19" s="4">
         <f>(G19+H19)/I19</f>
-        <v>1.064516129032258</v>
+        <v>2.86046511627907</v>
       </c>
       <c r="K19" s="1">
-        <v>14668</v>
+        <v>32785</v>
       </c>
       <c r="L19" s="1">
-        <v>15865</v>
+        <v>24372</v>
       </c>
       <c r="M19" s="1">
         <f>K19-L19</f>
-        <v>-1197</v>
+        <v>8413</v>
       </c>
       <c r="N19" s="5">
         <f>K19/F19</f>
-        <v>488.93333333333334</v>
+        <v>745.11363636363637</v>
       </c>
       <c r="O19" s="6">
-        <v>0.5</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="P19" s="6">
-        <v>0.66700000000000004</v>
+        <v>0.69</v>
       </c>
       <c r="Q19" s="7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1446,44 +1491,47 @@
       <c r="D20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>18</v>
+      <c r="E20" s="3">
+        <v>23</v>
+      </c>
+      <c r="F20" s="1">
+        <v>36</v>
+      </c>
+      <c r="G20" s="1">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1">
+        <v>31</v>
+      </c>
+      <c r="I20" s="1">
+        <v>37</v>
+      </c>
+      <c r="J20" s="4">
+        <f>(G20+H20)/I20</f>
+        <v>1.5135135135135136</v>
+      </c>
+      <c r="K20" s="1">
+        <v>20473</v>
+      </c>
+      <c r="L20" s="1">
+        <v>23721</v>
+      </c>
+      <c r="M20" s="1">
+        <f>K20-L20</f>
+        <v>-3248</v>
+      </c>
+      <c r="N20" s="5">
+        <f>K20/F20</f>
+        <v>568.69444444444446</v>
+      </c>
+      <c r="O20" s="6">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="P20" s="6">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1494,46 +1542,46 @@
         <v>20</v>
       </c>
       <c r="E21" s="3">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G21" s="1">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H21" s="1">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="I21" s="1">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J21" s="4">
         <f>(G21+H21)/I21</f>
-        <v>0.58333333333333337</v>
+        <v>2.4318181818181817</v>
       </c>
       <c r="K21" s="1">
-        <v>12794</v>
+        <v>28624</v>
       </c>
       <c r="L21" s="1">
-        <v>17451</v>
+        <v>26622</v>
       </c>
       <c r="M21" s="1">
         <f>K21-L21</f>
-        <v>-4657</v>
+        <v>2002</v>
       </c>
       <c r="N21" s="5">
         <f>K21/F21</f>
-        <v>533.08333333333337</v>
+        <v>650.5454545454545</v>
       </c>
       <c r="O21" s="6">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="P21" s="6">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="Q21" s="7">
         <v>0.25</v>
-      </c>
-      <c r="P21" s="6">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1543,44 +1591,47 @@
       <c r="D22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>18</v>
+      <c r="E22" s="3">
+        <v>14</v>
+      </c>
+      <c r="F22" s="1">
+        <v>44</v>
+      </c>
+      <c r="G22" s="1">
+        <v>32</v>
+      </c>
+      <c r="H22" s="1">
+        <v>50</v>
+      </c>
+      <c r="I22" s="1">
+        <v>46</v>
+      </c>
+      <c r="J22" s="4">
+        <f>(G22+H22)/I22</f>
+        <v>1.7826086956521738</v>
+      </c>
+      <c r="K22" s="1">
+        <v>25908</v>
+      </c>
+      <c r="L22" s="1">
+        <v>34120</v>
+      </c>
+      <c r="M22" s="1">
+        <f>K22-L22</f>
+        <v>-8212</v>
+      </c>
+      <c r="N22" s="5">
+        <f>K22/F22</f>
+        <v>588.81818181818187</v>
+      </c>
+      <c r="O22" s="6">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="P22" s="6">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>0.222</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1728,7 +1779,7 @@
     </row>
     <row r="26" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1736,43 +1787,43 @@
         <v>16</v>
       </c>
       <c r="E26" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F26" s="1">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G26" s="1">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H26" s="1">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I26" s="1">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="J26" s="4">
         <f>(G26+H26)/I26</f>
-        <v>1.5961538461538463</v>
+        <v>1.0857142857142856</v>
       </c>
       <c r="K26" s="1">
-        <v>27632</v>
+        <v>15917</v>
       </c>
       <c r="L26" s="1">
-        <v>24475</v>
+        <v>19533</v>
       </c>
       <c r="M26" s="1">
         <f>K26-L26</f>
-        <v>3157</v>
+        <v>-3616</v>
       </c>
       <c r="N26" s="5">
         <f>K26/F26</f>
-        <v>628</v>
+        <v>530.56666666666672</v>
       </c>
       <c r="O26" s="6">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="P26" s="6">
-        <v>0.316</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="Q26" s="7">
         <v>0</v>
@@ -1786,46 +1837,46 @@
         <v>17</v>
       </c>
       <c r="E27" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F27" s="1">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H27" s="1">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I27" s="1">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J27" s="4">
         <f>(G27+H27)/I27</f>
-        <v>2.9230769230769229</v>
+        <v>1.064516129032258</v>
       </c>
       <c r="K27" s="1">
-        <v>36750</v>
+        <v>14668</v>
       </c>
       <c r="L27" s="1">
-        <v>31921</v>
+        <v>15865</v>
       </c>
       <c r="M27" s="1">
         <f>K27-L27</f>
-        <v>4829</v>
+        <v>-1197</v>
       </c>
       <c r="N27" s="5">
         <f>K27/F27</f>
-        <v>835.22727272727275</v>
+        <v>488.93333333333334</v>
       </c>
       <c r="O27" s="6">
-        <v>0.72699999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="P27" s="6">
-        <v>0.71899999999999997</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="Q27" s="7">
-        <v>0.34799999999999998</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1835,47 +1886,44 @@
       <c r="D28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="3">
-        <v>13</v>
-      </c>
-      <c r="F28" s="1">
-        <v>44</v>
-      </c>
-      <c r="G28" s="1">
-        <v>28</v>
-      </c>
-      <c r="H28" s="1">
-        <v>50</v>
-      </c>
-      <c r="I28" s="1">
-        <v>42</v>
-      </c>
-      <c r="J28" s="4">
-        <f>(G28+H28)/I28</f>
-        <v>1.8571428571428572</v>
-      </c>
-      <c r="K28" s="1">
-        <v>24161</v>
-      </c>
-      <c r="L28" s="1">
-        <v>29365</v>
-      </c>
-      <c r="M28" s="1">
-        <f>K28-L28</f>
-        <v>-5204</v>
-      </c>
-      <c r="N28" s="5">
-        <f>K28/F28</f>
-        <v>549.11363636363637</v>
-      </c>
-      <c r="O28" s="6">
-        <v>0.61399999999999999</v>
-      </c>
-      <c r="P28" s="6">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="Q28" s="7">
-        <v>0.2</v>
+      <c r="E28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1886,46 +1934,46 @@
         <v>20</v>
       </c>
       <c r="E29" s="3">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F29" s="1">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G29" s="1">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="H29" s="1">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="I29" s="1">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J29" s="4">
         <f>(G29+H29)/I29</f>
-        <v>2.4</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="K29" s="1">
-        <v>26072</v>
+        <v>12794</v>
       </c>
       <c r="L29" s="1">
-        <v>25520</v>
+        <v>17451</v>
       </c>
       <c r="M29" s="1">
         <f>K29-L29</f>
-        <v>552</v>
+        <v>-4657</v>
       </c>
       <c r="N29" s="5">
         <f>K29/F29</f>
-        <v>592.5454545454545</v>
+        <v>533.08333333333337</v>
       </c>
       <c r="O29" s="6">
-        <v>0.38600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="P29" s="6">
-        <v>0.35299999999999998</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="Q29" s="7">
-        <v>0.66700000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1935,47 +1983,44 @@
       <c r="D30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="3">
-        <v>20</v>
-      </c>
-      <c r="F30" s="1">
-        <v>44</v>
-      </c>
-      <c r="G30" s="1">
-        <v>30</v>
-      </c>
-      <c r="H30" s="1">
-        <v>33</v>
-      </c>
-      <c r="I30" s="1">
-        <v>42</v>
-      </c>
-      <c r="J30" s="4">
-        <f>(G30+H30)/I30</f>
-        <v>1.5</v>
-      </c>
-      <c r="K30" s="1">
-        <v>24499</v>
-      </c>
-      <c r="L30" s="1">
-        <v>29663</v>
-      </c>
-      <c r="M30" s="1">
-        <f>K30-L30</f>
-        <v>-5164</v>
-      </c>
-      <c r="N30" s="5">
-        <f>K30/F30</f>
-        <v>556.7954545454545</v>
-      </c>
-      <c r="O30" s="6">
-        <v>0.47699999999999998</v>
-      </c>
-      <c r="P30" s="6">
-        <v>0.38100000000000001</v>
-      </c>
-      <c r="Q30" s="7">
-        <v>0.375</v>
+      <c r="E30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q30" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -2123,7 +2168,7 @@
     </row>
     <row r="34" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -2131,46 +2176,46 @@
         <v>16</v>
       </c>
       <c r="E34" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F34" s="1">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G34" s="1">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H34" s="1">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I34" s="1">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="J34" s="4">
         <f>(G34+H34)/I34</f>
-        <v>3.125</v>
+        <v>1.5961538461538463</v>
       </c>
       <c r="K34" s="1">
-        <v>13896</v>
+        <v>27632</v>
       </c>
       <c r="L34" s="1">
-        <v>13984</v>
+        <v>24475</v>
       </c>
       <c r="M34" s="1">
         <f>K34-L34</f>
-        <v>-88</v>
+        <v>3157</v>
       </c>
       <c r="N34" s="5">
         <f>K34/F34</f>
-        <v>731.36842105263156</v>
+        <v>628</v>
       </c>
       <c r="O34" s="6">
-        <v>0.73699999999999999</v>
+        <v>0.432</v>
       </c>
       <c r="P34" s="6">
-        <v>0.64300000000000002</v>
+        <v>0.316</v>
       </c>
       <c r="Q34" s="7">
-        <v>0.33300000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2181,46 +2226,46 @@
         <v>17</v>
       </c>
       <c r="E35" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G35" s="1">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H35" s="1">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="I35" s="1">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="J35" s="4">
         <f>(G35+H35)/I35</f>
-        <v>1.8888888888888888</v>
+        <v>2.9230769230769229</v>
       </c>
       <c r="K35" s="1">
-        <v>8042</v>
+        <v>36750</v>
       </c>
       <c r="L35" s="1">
-        <v>11394</v>
+        <v>31921</v>
       </c>
       <c r="M35" s="1">
         <f>K35-L35</f>
-        <v>-3352</v>
+        <v>4829</v>
       </c>
       <c r="N35" s="5">
         <f>K35/F35</f>
-        <v>423.26315789473682</v>
+        <v>835.22727272727275</v>
       </c>
       <c r="O35" s="6">
-        <v>0.63200000000000001</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="P35" s="6">
-        <v>0.83299999999999996</v>
+        <v>0.71899999999999997</v>
       </c>
       <c r="Q35" s="7">
-        <v>0.1</v>
+        <v>0.34799999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2231,46 +2276,46 @@
         <v>19</v>
       </c>
       <c r="E36" s="3">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="G36" s="1">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H36" s="1">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="I36" s="1">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="J36" s="4">
         <f>(G36+H36)/I36</f>
-        <v>1.1000000000000001</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="K36" s="1">
-        <v>2714</v>
+        <v>24161</v>
       </c>
       <c r="L36" s="1">
-        <v>3747</v>
+        <v>29365</v>
       </c>
       <c r="M36" s="1">
         <f>K36-L36</f>
-        <v>-1033</v>
+        <v>-5204</v>
       </c>
       <c r="N36" s="5">
         <f>K36/F36</f>
-        <v>271.39999999999998</v>
+        <v>549.11363636363637</v>
       </c>
       <c r="O36" s="6">
-        <v>0.3</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="P36" s="6">
-        <v>1</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="Q36" s="7">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2281,46 +2326,46 @@
         <v>20</v>
       </c>
       <c r="E37" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G37" s="1">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H37" s="1">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I37" s="1">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J37" s="4">
         <f>(G37+H37)/I37</f>
-        <v>1.3913043478260869</v>
+        <v>2.4</v>
       </c>
       <c r="K37" s="1">
-        <v>12276</v>
+        <v>26072</v>
       </c>
       <c r="L37" s="1">
-        <v>13224</v>
+        <v>25520</v>
       </c>
       <c r="M37" s="1">
         <f>K37-L37</f>
-        <v>-948</v>
+        <v>552</v>
       </c>
       <c r="N37" s="5">
         <f>K37/F37</f>
-        <v>613.79999999999995</v>
+        <v>592.5454545454545</v>
       </c>
       <c r="O37" s="6">
-        <v>0.45</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="P37" s="6">
-        <v>0.33300000000000002</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="Q37" s="7">
-        <v>0</v>
+        <v>0.66700000000000004</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2330,44 +2375,47 @@
       <c r="D38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N38" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>18</v>
+      <c r="E38" s="3">
+        <v>20</v>
+      </c>
+      <c r="F38" s="1">
+        <v>44</v>
+      </c>
+      <c r="G38" s="1">
+        <v>30</v>
+      </c>
+      <c r="H38" s="1">
+        <v>33</v>
+      </c>
+      <c r="I38" s="1">
+        <v>42</v>
+      </c>
+      <c r="J38" s="4">
+        <f>(G38+H38)/I38</f>
+        <v>1.5</v>
+      </c>
+      <c r="K38" s="1">
+        <v>24499</v>
+      </c>
+      <c r="L38" s="1">
+        <v>29663</v>
+      </c>
+      <c r="M38" s="1">
+        <f>K38-L38</f>
+        <v>-5164</v>
+      </c>
+      <c r="N38" s="5">
+        <f>K38/F38</f>
+        <v>556.7954545454545</v>
+      </c>
+      <c r="O38" s="6">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="P38" s="6">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>0.375</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -2515,7 +2563,7 @@
     </row>
     <row r="42" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -2523,46 +2571,46 @@
         <v>16</v>
       </c>
       <c r="E42" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F42" s="1">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G42" s="1">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H42" s="1">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I42" s="1">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="J42" s="4">
         <f>(G42+H42)/I42</f>
-        <v>1.5111111111111111</v>
+        <v>3.125</v>
       </c>
       <c r="K42" s="1">
-        <v>21875</v>
+        <v>13896</v>
       </c>
       <c r="L42" s="1">
-        <v>28142</v>
+        <v>13984</v>
       </c>
       <c r="M42" s="1">
         <f>K42-L42</f>
-        <v>-6267</v>
+        <v>-88</v>
       </c>
       <c r="N42" s="5">
         <f>K42/F42</f>
-        <v>607.63888888888891</v>
+        <v>731.36842105263156</v>
       </c>
       <c r="O42" s="6">
-        <v>0.63900000000000001</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="P42" s="6">
-        <v>0.65200000000000002</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="Q42" s="7">
-        <v>0.13300000000000001</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2572,44 +2620,47 @@
       <c r="D43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q43" s="7" t="s">
-        <v>18</v>
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="1">
+        <v>19</v>
+      </c>
+      <c r="G43" s="1">
+        <v>12</v>
+      </c>
+      <c r="H43" s="1">
+        <v>22</v>
+      </c>
+      <c r="I43" s="1">
+        <v>18</v>
+      </c>
+      <c r="J43" s="4">
+        <f>(G43+H43)/I43</f>
+        <v>1.8888888888888888</v>
+      </c>
+      <c r="K43" s="1">
+        <v>8042</v>
+      </c>
+      <c r="L43" s="1">
+        <v>11394</v>
+      </c>
+      <c r="M43" s="1">
+        <f>K43-L43</f>
+        <v>-3352</v>
+      </c>
+      <c r="N43" s="5">
+        <f>K43/F43</f>
+        <v>423.26315789473682</v>
+      </c>
+      <c r="O43" s="6">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="P43" s="6">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2619,44 +2670,47 @@
       <c r="D44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N44" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q44" s="7" t="s">
-        <v>18</v>
+      <c r="E44" s="3">
+        <v>37</v>
+      </c>
+      <c r="F44" s="1">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1">
+        <v>3</v>
+      </c>
+      <c r="H44" s="1">
+        <v>8</v>
+      </c>
+      <c r="I44" s="1">
+        <v>10</v>
+      </c>
+      <c r="J44" s="4">
+        <f>(G44+H44)/I44</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K44" s="1">
+        <v>2714</v>
+      </c>
+      <c r="L44" s="1">
+        <v>3747</v>
+      </c>
+      <c r="M44" s="1">
+        <f>K44-L44</f>
+        <v>-1033</v>
+      </c>
+      <c r="N44" s="5">
+        <f>K44/F44</f>
+        <v>271.39999999999998</v>
+      </c>
+      <c r="O44" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="P44" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2667,46 +2721,46 @@
         <v>20</v>
       </c>
       <c r="E45" s="3">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F45" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G45" s="1">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H45" s="1">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="I45" s="1">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J45" s="4">
         <f>(G45+H45)/I45</f>
-        <v>2.9655172413793105</v>
+        <v>1.3913043478260869</v>
       </c>
       <c r="K45" s="1">
-        <v>15090</v>
+        <v>12276</v>
       </c>
       <c r="L45" s="1">
-        <v>13600</v>
+        <v>13224</v>
       </c>
       <c r="M45" s="1">
         <f>K45-L45</f>
-        <v>1490</v>
+        <v>-948</v>
       </c>
       <c r="N45" s="5">
         <f>K45/F45</f>
-        <v>503</v>
+        <v>613.79999999999995</v>
       </c>
       <c r="O45" s="6">
-        <v>0.56699999999999995</v>
+        <v>0.45</v>
       </c>
       <c r="P45" s="6">
-        <v>0.52900000000000003</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="Q45" s="7">
-        <v>0.33300000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2901,7 +2955,7 @@
     </row>
     <row r="50" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -2909,46 +2963,46 @@
         <v>16</v>
       </c>
       <c r="E50" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G50" s="1">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H50" s="1">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="I50" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J50" s="4">
-        <f t="shared" ref="J50:J55" si="0">(G50+H50)/I50</f>
-        <v>3.9249999999999998</v>
+        <f>(G50+H50)/I50</f>
+        <v>1.5111111111111111</v>
       </c>
       <c r="K50" s="1">
-        <v>37862</v>
+        <v>21875</v>
       </c>
       <c r="L50" s="1">
-        <v>35113</v>
+        <v>28142</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" ref="M50:M55" si="1">K50-L50</f>
-        <v>2749</v>
+        <f>K50-L50</f>
+        <v>-6267</v>
       </c>
       <c r="N50" s="5">
-        <f t="shared" ref="N50:N55" si="2">K50/F50</f>
-        <v>880.51162790697674</v>
+        <f>K50/F50</f>
+        <v>607.63888888888891</v>
       </c>
       <c r="O50" s="6">
-        <v>0.81399999999999995</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="P50" s="6">
-        <v>0.629</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="Q50" s="7">
-        <v>0.36399999999999999</v>
+        <v>0.13300000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2958,47 +3012,44 @@
       <c r="D51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="3">
-        <v>6</v>
-      </c>
-      <c r="F51" s="1">
-        <v>43</v>
-      </c>
-      <c r="G51" s="1">
-        <v>23</v>
-      </c>
-      <c r="H51" s="1">
-        <v>82</v>
-      </c>
-      <c r="I51" s="1">
-        <v>45</v>
-      </c>
-      <c r="J51" s="4">
-        <f t="shared" si="0"/>
-        <v>2.3333333333333335</v>
-      </c>
-      <c r="K51" s="1">
-        <v>16801</v>
-      </c>
-      <c r="L51" s="1">
-        <v>18525</v>
-      </c>
-      <c r="M51" s="1">
-        <f t="shared" si="1"/>
-        <v>-1724</v>
-      </c>
-      <c r="N51" s="5">
-        <f t="shared" si="2"/>
-        <v>390.72093023255815</v>
-      </c>
-      <c r="O51" s="6">
-        <v>0.442</v>
-      </c>
-      <c r="P51" s="6">
-        <v>0.52600000000000002</v>
-      </c>
-      <c r="Q51" s="7">
-        <v>0.3</v>
+      <c r="E51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q51" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3008,47 +3059,44 @@
       <c r="D52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E52" s="3">
-        <v>8</v>
-      </c>
-      <c r="F52" s="1">
-        <v>43</v>
-      </c>
-      <c r="G52" s="1">
-        <v>26</v>
-      </c>
-      <c r="H52" s="1">
-        <v>56</v>
-      </c>
-      <c r="I52" s="1">
-        <v>44</v>
-      </c>
-      <c r="J52" s="4">
-        <f t="shared" si="0"/>
-        <v>1.8636363636363635</v>
-      </c>
-      <c r="K52" s="1">
-        <v>23435</v>
-      </c>
-      <c r="L52" s="1">
-        <v>27828</v>
-      </c>
-      <c r="M52" s="1">
-        <f t="shared" si="1"/>
-        <v>-4393</v>
-      </c>
-      <c r="N52" s="5">
-        <f t="shared" si="2"/>
-        <v>545</v>
-      </c>
-      <c r="O52" s="6">
-        <v>0.60499999999999998</v>
-      </c>
-      <c r="P52" s="6">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="Q52" s="7">
-        <v>0.214</v>
+      <c r="E52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q52" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3059,46 +3107,46 @@
         <v>20</v>
       </c>
       <c r="E53" s="3">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F53" s="1">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G53" s="1">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="H53" s="1">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I53" s="1">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J53" s="4">
-        <f t="shared" si="0"/>
-        <v>2.7674418604651163</v>
+        <f>(G53+H53)/I53</f>
+        <v>2.9655172413793105</v>
       </c>
       <c r="K53" s="1">
-        <v>29212</v>
+        <v>15090</v>
       </c>
       <c r="L53" s="1">
-        <v>28531</v>
+        <v>13600</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="1"/>
-        <v>681</v>
+        <f>K53-L53</f>
+        <v>1490</v>
       </c>
       <c r="N53" s="5">
-        <f t="shared" si="2"/>
-        <v>679.34883720930236</v>
+        <f>K53/F53</f>
+        <v>503</v>
       </c>
       <c r="O53" s="6">
-        <v>0.69799999999999995</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="P53" s="6">
-        <v>0.56699999999999995</v>
+        <v>0.52900000000000003</v>
       </c>
       <c r="Q53" s="7">
-        <v>0.23499999999999999</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3108,47 +3156,44 @@
       <c r="D54" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E54" s="3">
-        <v>12</v>
-      </c>
-      <c r="F54" s="1">
-        <v>43</v>
-      </c>
-      <c r="G54" s="1">
-        <v>32</v>
-      </c>
-      <c r="H54" s="1">
-        <v>40</v>
-      </c>
-      <c r="I54" s="1">
-        <v>45</v>
-      </c>
-      <c r="J54" s="4">
-        <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-      <c r="K54" s="1">
-        <v>20604</v>
-      </c>
-      <c r="L54" s="1">
-        <v>25152</v>
-      </c>
-      <c r="M54" s="1">
-        <f t="shared" si="1"/>
-        <v>-4548</v>
-      </c>
-      <c r="N54" s="5">
-        <f t="shared" si="2"/>
-        <v>479.16279069767444</v>
-      </c>
-      <c r="O54" s="6">
-        <v>0.628</v>
-      </c>
-      <c r="P54" s="6">
-        <v>0.40699999999999997</v>
-      </c>
-      <c r="Q54" s="7">
-        <v>9.0999999999999998E-2</v>
+      <c r="E54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q54" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -3158,47 +3203,44 @@
       <c r="D55" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E55" s="3">
-        <v>27</v>
-      </c>
-      <c r="F55" s="1">
-        <v>18</v>
-      </c>
-      <c r="G55" s="1">
-        <v>10</v>
-      </c>
-      <c r="H55" s="1">
-        <v>19</v>
-      </c>
-      <c r="I55" s="1">
-        <v>18</v>
-      </c>
-      <c r="J55" s="4">
-        <f t="shared" si="0"/>
-        <v>1.6111111111111112</v>
-      </c>
-      <c r="K55" s="1">
-        <v>10898</v>
-      </c>
-      <c r="L55" s="1">
-        <v>9545</v>
-      </c>
-      <c r="M55" s="1">
-        <f t="shared" si="1"/>
-        <v>1353</v>
-      </c>
-      <c r="N55" s="5">
-        <f t="shared" si="2"/>
-        <v>605.44444444444446</v>
-      </c>
-      <c r="O55" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="P55" s="6">
-        <v>0.44400000000000001</v>
-      </c>
-      <c r="Q55" s="7">
-        <v>0</v>
+      <c r="E55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N55" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q55" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3299,7 +3341,7 @@
     </row>
     <row r="58" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -3307,46 +3349,46 @@
         <v>16</v>
       </c>
       <c r="E58" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F58" s="1">
         <v>43</v>
       </c>
       <c r="G58" s="1">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H58" s="1">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="I58" s="1">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J58" s="4">
-        <f>(G58+H58)/I58</f>
-        <v>1.8235294117647058</v>
+        <f t="shared" ref="J58:J63" si="0">(G58+H58)/I58</f>
+        <v>3.9249999999999998</v>
       </c>
       <c r="K58" s="1">
-        <v>29785</v>
+        <v>37862</v>
       </c>
       <c r="L58" s="1">
-        <v>36524</v>
+        <v>35113</v>
       </c>
       <c r="M58" s="1">
-        <f>K58-L58</f>
-        <v>-6739</v>
+        <f t="shared" ref="M58:M63" si="1">K58-L58</f>
+        <v>2749</v>
       </c>
       <c r="N58" s="5">
-        <f>K58/F58</f>
-        <v>692.67441860465112</v>
+        <f t="shared" ref="N58:N63" si="2">K58/F58</f>
+        <v>880.51162790697674</v>
       </c>
       <c r="O58" s="6">
-        <v>0.65100000000000002</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="P58" s="6">
-        <v>0.57099999999999995</v>
+        <v>0.629</v>
       </c>
       <c r="Q58" s="7">
-        <v>6.3E-2</v>
+        <v>0.36399999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3356,44 +3398,47 @@
       <c r="D59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N59" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q59" s="7" t="s">
-        <v>18</v>
+      <c r="E59" s="3">
+        <v>6</v>
+      </c>
+      <c r="F59" s="1">
+        <v>43</v>
+      </c>
+      <c r="G59" s="1">
+        <v>23</v>
+      </c>
+      <c r="H59" s="1">
+        <v>82</v>
+      </c>
+      <c r="I59" s="1">
+        <v>45</v>
+      </c>
+      <c r="J59" s="4">
+        <f t="shared" si="0"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="K59" s="1">
+        <v>16801</v>
+      </c>
+      <c r="L59" s="1">
+        <v>18525</v>
+      </c>
+      <c r="M59" s="1">
+        <f t="shared" si="1"/>
+        <v>-1724</v>
+      </c>
+      <c r="N59" s="5">
+        <f t="shared" si="2"/>
+        <v>390.72093023255815</v>
+      </c>
+      <c r="O59" s="6">
+        <v>0.442</v>
+      </c>
+      <c r="P59" s="6">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="Q59" s="7">
+        <v>0.3</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3404,46 +3449,46 @@
         <v>19</v>
       </c>
       <c r="E60" s="3">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1">
+        <v>43</v>
+      </c>
+      <c r="G60" s="1">
         <v>26</v>
       </c>
-      <c r="G60" s="1">
-        <v>27</v>
-      </c>
       <c r="H60" s="1">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I60" s="1">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J60" s="4">
-        <f>(G60+H60)/I60</f>
-        <v>1.5384615384615385</v>
+        <f t="shared" si="0"/>
+        <v>1.8636363636363635</v>
       </c>
       <c r="K60" s="1">
-        <v>12306</v>
+        <v>23435</v>
       </c>
       <c r="L60" s="1">
-        <v>17033</v>
+        <v>27828</v>
       </c>
       <c r="M60" s="1">
-        <f>K60-L60</f>
-        <v>-4727</v>
+        <f t="shared" si="1"/>
+        <v>-4393</v>
       </c>
       <c r="N60" s="5">
-        <f>K60/F60</f>
-        <v>473.30769230769232</v>
+        <f t="shared" si="2"/>
+        <v>545</v>
       </c>
       <c r="O60" s="6">
-        <v>0.46200000000000002</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="P60" s="6">
-        <v>0.33300000000000002</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="Q60" s="7">
-        <v>0</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3454,46 +3499,46 @@
         <v>20</v>
       </c>
       <c r="E61" s="3">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F61" s="1">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G61" s="1">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H61" s="1">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="I61" s="1">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J61" s="4">
-        <f>(G61+H61)/I61</f>
-        <v>1.5517241379310345</v>
+        <f t="shared" si="0"/>
+        <v>2.7674418604651163</v>
       </c>
       <c r="K61" s="1">
-        <v>16682</v>
+        <v>29212</v>
       </c>
       <c r="L61" s="1">
-        <v>20834</v>
+        <v>28531</v>
       </c>
       <c r="M61" s="1">
-        <f>K61-L61</f>
-        <v>-4152</v>
+        <f t="shared" si="1"/>
+        <v>681</v>
       </c>
       <c r="N61" s="5">
-        <f>K61/F61</f>
-        <v>641.61538461538464</v>
+        <f t="shared" si="2"/>
+        <v>679.34883720930236</v>
       </c>
       <c r="O61" s="6">
-        <v>0.46200000000000002</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="P61" s="6">
-        <v>0.58299999999999996</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="Q61" s="7">
-        <v>0</v>
+        <v>0.23499999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3503,44 +3548,47 @@
       <c r="D62" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N62" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q62" s="7" t="s">
-        <v>18</v>
+      <c r="E62" s="3">
+        <v>12</v>
+      </c>
+      <c r="F62" s="1">
+        <v>43</v>
+      </c>
+      <c r="G62" s="1">
+        <v>32</v>
+      </c>
+      <c r="H62" s="1">
+        <v>40</v>
+      </c>
+      <c r="I62" s="1">
+        <v>45</v>
+      </c>
+      <c r="J62" s="4">
+        <f t="shared" si="0"/>
+        <v>1.6</v>
+      </c>
+      <c r="K62" s="1">
+        <v>20604</v>
+      </c>
+      <c r="L62" s="1">
+        <v>25152</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="1"/>
+        <v>-4548</v>
+      </c>
+      <c r="N62" s="5">
+        <f t="shared" si="2"/>
+        <v>479.16279069767444</v>
+      </c>
+      <c r="O62" s="6">
+        <v>0.628</v>
+      </c>
+      <c r="P62" s="6">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="Q62" s="7">
+        <v>9.0999999999999998E-2</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -3551,46 +3599,46 @@
         <v>22</v>
       </c>
       <c r="E63" s="3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F63" s="1">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G63" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H63" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I63" s="1">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J63" s="4">
-        <f>(G63+H63)/I63</f>
-        <v>1.4230769230769231</v>
+        <f t="shared" si="0"/>
+        <v>1.6111111111111112</v>
       </c>
       <c r="K63" s="1">
-        <v>13496</v>
+        <v>10898</v>
       </c>
       <c r="L63" s="1">
-        <v>15639</v>
+        <v>9545</v>
       </c>
       <c r="M63" s="1">
-        <f>K63-L63</f>
-        <v>-2143</v>
+        <f t="shared" si="1"/>
+        <v>1353</v>
       </c>
       <c r="N63" s="5">
-        <f>K63/F63</f>
-        <v>519.07692307692309</v>
+        <f t="shared" si="2"/>
+        <v>605.44444444444446</v>
       </c>
       <c r="O63" s="6">
-        <v>0.38500000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="P63" s="6">
-        <v>0.2</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="Q63" s="7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3691,7 +3739,7 @@
     </row>
     <row r="66" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -3699,46 +3747,46 @@
         <v>16</v>
       </c>
       <c r="E66" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F66" s="1">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G66" s="1">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H66" s="1">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I66" s="1">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="J66" s="4">
         <f>(G66+H66)/I66</f>
-        <v>1.8611111111111112</v>
+        <v>1.8235294117647058</v>
       </c>
       <c r="K66" s="1">
-        <v>18416</v>
+        <v>29785</v>
       </c>
       <c r="L66" s="1">
-        <v>18431</v>
+        <v>36524</v>
       </c>
       <c r="M66" s="1">
         <f>K66-L66</f>
-        <v>-15</v>
+        <v>-6739</v>
       </c>
       <c r="N66" s="5">
         <f>K66/F66</f>
-        <v>541.64705882352939</v>
+        <v>692.67441860465112</v>
       </c>
       <c r="O66" s="6">
-        <v>0.64700000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="P66" s="6">
-        <v>0.54500000000000004</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="Q66" s="7">
-        <v>8.3000000000000004E-2</v>
+        <v>6.3E-2</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3748,47 +3796,44 @@
       <c r="D67" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E67" s="3">
-        <v>30</v>
-      </c>
-      <c r="F67" s="1">
-        <v>30</v>
-      </c>
-      <c r="G67" s="1">
-        <v>10</v>
-      </c>
-      <c r="H67" s="1">
-        <v>33</v>
-      </c>
-      <c r="I67" s="1">
-        <v>28</v>
-      </c>
-      <c r="J67" s="4">
-        <f>(G67+H67)/I67</f>
-        <v>1.5357142857142858</v>
-      </c>
-      <c r="K67" s="1">
-        <v>9439</v>
-      </c>
-      <c r="L67" s="1">
-        <v>10450</v>
-      </c>
-      <c r="M67" s="1">
-        <f>K67-L67</f>
-        <v>-1011</v>
-      </c>
-      <c r="N67" s="5">
-        <f>K67/F67</f>
-        <v>314.63333333333333</v>
-      </c>
-      <c r="O67" s="6">
-        <v>0.26740000000000003</v>
-      </c>
-      <c r="P67" s="6">
-        <v>0.125</v>
-      </c>
-      <c r="Q67" s="7">
-        <v>1</v>
+      <c r="E67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N67" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q67" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3799,46 +3844,46 @@
         <v>19</v>
       </c>
       <c r="E68" s="3">
+        <v>35</v>
+      </c>
+      <c r="F68" s="1">
+        <v>26</v>
+      </c>
+      <c r="G68" s="1">
+        <v>27</v>
+      </c>
+      <c r="H68" s="1">
         <v>13</v>
       </c>
-      <c r="F68" s="1">
-        <v>40</v>
-      </c>
-      <c r="G68" s="1">
-        <v>12</v>
-      </c>
-      <c r="H68" s="1">
-        <v>61</v>
-      </c>
       <c r="I68" s="1">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J68" s="4">
         <f>(G68+H68)/I68</f>
-        <v>1.8717948717948718</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="K68" s="1">
-        <v>17165</v>
+        <v>12306</v>
       </c>
       <c r="L68" s="1">
-        <v>16406</v>
+        <v>17033</v>
       </c>
       <c r="M68" s="1">
         <f>K68-L68</f>
-        <v>759</v>
+        <v>-4727</v>
       </c>
       <c r="N68" s="5">
         <f>K68/F68</f>
-        <v>429.125</v>
+        <v>473.30769230769232</v>
       </c>
       <c r="O68" s="6">
-        <v>0.52500000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="P68" s="6">
-        <v>0.42899999999999999</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="Q68" s="7">
-        <v>0.111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3849,43 +3894,43 @@
         <v>20</v>
       </c>
       <c r="E69" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F69" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G69" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H69" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I69" s="1">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J69" s="4">
         <f>(G69+H69)/I69</f>
-        <v>1.125</v>
+        <v>1.5517241379310345</v>
       </c>
       <c r="K69" s="1">
-        <v>7397</v>
+        <v>16682</v>
       </c>
       <c r="L69" s="1">
-        <v>10028</v>
+        <v>20834</v>
       </c>
       <c r="M69" s="1">
         <f>K69-L69</f>
-        <v>-2631</v>
+        <v>-4152</v>
       </c>
       <c r="N69" s="5">
         <f>K69/F69</f>
-        <v>308.20833333333331</v>
+        <v>641.61538461538464</v>
       </c>
       <c r="O69" s="6">
-        <v>0.20799999999999999</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="P69" s="6">
-        <v>0</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="Q69" s="7">
         <v>0</v>
@@ -3946,46 +3991,46 @@
         <v>22</v>
       </c>
       <c r="E71" s="3">
+        <v>38</v>
+      </c>
+      <c r="F71" s="1">
+        <v>26</v>
+      </c>
+      <c r="G71" s="1">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1">
         <v>22</v>
       </c>
-      <c r="F71" s="1">
-        <v>30</v>
-      </c>
-      <c r="G71" s="1">
-        <v>21</v>
-      </c>
-      <c r="H71" s="1">
-        <v>47</v>
-      </c>
       <c r="I71" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J71" s="4">
         <f>(G71+H71)/I71</f>
-        <v>2.193548387096774</v>
+        <v>1.4230769230769231</v>
       </c>
       <c r="K71" s="1">
-        <v>12267</v>
+        <v>13496</v>
       </c>
       <c r="L71" s="1">
-        <v>13046</v>
+        <v>15639</v>
       </c>
       <c r="M71" s="1">
         <f>K71-L71</f>
-        <v>-779</v>
+        <v>-2143</v>
       </c>
       <c r="N71" s="5">
         <f>K71/F71</f>
-        <v>408.9</v>
+        <v>519.07692307692309</v>
       </c>
       <c r="O71" s="6">
-        <v>0.46700000000000003</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="P71" s="6">
-        <v>0.42899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q71" s="7">
-        <v>0.16700000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4086,7 +4131,7 @@
     </row>
     <row r="74" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -4094,46 +4139,46 @@
         <v>16</v>
       </c>
       <c r="E74" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G74" s="1">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H74" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I74" s="1">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J74" s="4">
         <f>(G74+H74)/I74</f>
-        <v>2.4102564102564101</v>
+        <v>1.8611111111111112</v>
       </c>
       <c r="K74" s="1">
-        <v>26373</v>
+        <v>18416</v>
       </c>
       <c r="L74" s="1">
-        <v>24525</v>
+        <v>18431</v>
       </c>
       <c r="M74" s="1">
         <f>K74-L74</f>
-        <v>1848</v>
+        <v>-15</v>
       </c>
       <c r="N74" s="5">
         <f>K74/F74</f>
-        <v>643.2439024390244</v>
+        <v>541.64705882352939</v>
       </c>
       <c r="O74" s="6">
-        <v>0.65900000000000003</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="P74" s="6">
-        <v>0.59299999999999997</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="Q74" s="7">
-        <v>0.313</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4144,46 +4189,46 @@
         <v>17</v>
       </c>
       <c r="E75" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F75" s="1">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G75" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H75" s="1">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I75" s="1">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J75" s="4">
         <f>(G75+H75)/I75</f>
-        <v>2.0256410256410255</v>
+        <v>1.5357142857142858</v>
       </c>
       <c r="K75" s="1">
-        <v>25680</v>
+        <v>9439</v>
       </c>
       <c r="L75" s="1">
-        <v>22882</v>
+        <v>10450</v>
       </c>
       <c r="M75" s="1">
         <f>K75-L75</f>
-        <v>2798</v>
+        <v>-1011</v>
       </c>
       <c r="N75" s="5">
         <f>K75/F75</f>
-        <v>597.20930232558135</v>
+        <v>314.63333333333333</v>
       </c>
       <c r="O75" s="6">
-        <v>0.72099999999999997</v>
+        <v>0.26740000000000003</v>
       </c>
       <c r="P75" s="6">
-        <v>0.58099999999999996</v>
+        <v>0.125</v>
       </c>
       <c r="Q75" s="7">
-        <v>0.27800000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4194,46 +4239,46 @@
         <v>19</v>
       </c>
       <c r="E76" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F76" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G76" s="1">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H76" s="1">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="I76" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J76" s="4">
         <f>(G76+H76)/I76</f>
-        <v>1.975609756097561</v>
+        <v>1.8717948717948718</v>
       </c>
       <c r="K76" s="1">
-        <v>23064</v>
+        <v>17165</v>
       </c>
       <c r="L76" s="1">
-        <v>23183</v>
+        <v>16406</v>
       </c>
       <c r="M76" s="1">
         <f>K76-L76</f>
-        <v>-119</v>
+        <v>759</v>
       </c>
       <c r="N76" s="5">
         <f>K76/F76</f>
-        <v>562.53658536585363</v>
+        <v>429.125</v>
       </c>
       <c r="O76" s="6">
-        <v>0.6</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="P76" s="6">
-        <v>0.54200000000000004</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="Q76" s="7">
-        <v>0.154</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4244,46 +4289,46 @@
         <v>20</v>
       </c>
       <c r="E77" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F77" s="1">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G77" s="1">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="H77" s="1">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I77" s="1">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J77" s="4">
         <f>(G77+H77)/I77</f>
-        <v>2.9772727272727271</v>
+        <v>1.125</v>
       </c>
       <c r="K77" s="1">
-        <v>29149</v>
+        <v>7397</v>
       </c>
       <c r="L77" s="1">
-        <v>23032</v>
+        <v>10028</v>
       </c>
       <c r="M77" s="1">
         <f>K77-L77</f>
-        <v>6117</v>
+        <v>-2631</v>
       </c>
       <c r="N77" s="5">
         <f>K77/F77</f>
-        <v>677.88372093023258</v>
+        <v>308.20833333333331</v>
       </c>
       <c r="O77" s="6">
-        <v>0.46500000000000002</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="P77" s="6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4293,47 +4338,44 @@
       <c r="D78" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E78" s="3">
-        <v>10</v>
-      </c>
-      <c r="F78" s="1">
-        <v>24</v>
-      </c>
-      <c r="G78" s="1">
-        <v>15</v>
-      </c>
-      <c r="H78" s="1">
-        <v>18</v>
-      </c>
-      <c r="I78" s="1">
-        <v>25</v>
-      </c>
-      <c r="J78" s="4">
-        <f>(G78+H78)/I78</f>
-        <v>1.32</v>
-      </c>
-      <c r="K78" s="1">
-        <v>10913</v>
-      </c>
-      <c r="L78" s="1">
-        <v>12933</v>
-      </c>
-      <c r="M78" s="1">
-        <f>K78-L78</f>
-        <v>-2020</v>
-      </c>
-      <c r="N78" s="5">
-        <f>K78/F78</f>
-        <v>454.70833333333331</v>
-      </c>
-      <c r="O78" s="6">
-        <v>0.55200000000000005</v>
-      </c>
-      <c r="P78" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Q78" s="7">
-        <v>0.25</v>
+      <c r="E78" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N78" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q78" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4343,44 +4385,47 @@
       <c r="D79" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N79" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O79" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P79" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q79" s="7" t="s">
-        <v>18</v>
+      <c r="E79" s="3">
+        <v>22</v>
+      </c>
+      <c r="F79" s="1">
+        <v>30</v>
+      </c>
+      <c r="G79" s="1">
+        <v>21</v>
+      </c>
+      <c r="H79" s="1">
+        <v>47</v>
+      </c>
+      <c r="I79" s="1">
+        <v>31</v>
+      </c>
+      <c r="J79" s="4">
+        <f>(G79+H79)/I79</f>
+        <v>2.193548387096774</v>
+      </c>
+      <c r="K79" s="1">
+        <v>12267</v>
+      </c>
+      <c r="L79" s="1">
+        <v>13046</v>
+      </c>
+      <c r="M79" s="1">
+        <f>K79-L79</f>
+        <v>-779</v>
+      </c>
+      <c r="N79" s="5">
+        <f>K79/F79</f>
+        <v>408.9</v>
+      </c>
+      <c r="O79" s="6">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="P79" s="6">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="Q79" s="7">
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4390,47 +4435,44 @@
       <c r="D80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E80" s="3">
-        <v>13</v>
-      </c>
-      <c r="F80" s="1">
-        <v>41</v>
-      </c>
-      <c r="G80" s="1">
-        <v>24</v>
-      </c>
-      <c r="H80" s="1">
-        <v>29</v>
-      </c>
-      <c r="I80" s="1">
-        <v>43</v>
-      </c>
-      <c r="J80" s="4">
-        <f>(G80+H80)/I80</f>
-        <v>1.2325581395348837</v>
-      </c>
-      <c r="K80" s="1">
-        <v>15126</v>
-      </c>
-      <c r="L80" s="1">
-        <v>15425</v>
-      </c>
-      <c r="M80" s="1">
-        <f>K80-L80</f>
-        <v>-299</v>
-      </c>
-      <c r="N80" s="5">
-        <f>K80/F80</f>
-        <v>368.92682926829269</v>
-      </c>
-      <c r="O80" s="6">
-        <v>0.51200000000000001</v>
-      </c>
-      <c r="P80" s="6">
-        <v>0.61899999999999999</v>
-      </c>
-      <c r="Q80" s="7">
-        <v>0</v>
+      <c r="E80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N80" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q80" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4484,51 +4526,54 @@
     </row>
     <row r="82" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
       <c r="D82" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N82" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q82" s="7" t="s">
-        <v>18</v>
+      <c r="E82" s="3">
+        <v>3</v>
+      </c>
+      <c r="F82" s="1">
+        <v>41</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45</v>
+      </c>
+      <c r="H82" s="1">
+        <v>49</v>
+      </c>
+      <c r="I82" s="1">
+        <v>39</v>
+      </c>
+      <c r="J82" s="4">
+        <f>(G82+H82)/I82</f>
+        <v>2.4102564102564101</v>
+      </c>
+      <c r="K82" s="1">
+        <v>26373</v>
+      </c>
+      <c r="L82" s="1">
+        <v>24525</v>
+      </c>
+      <c r="M82" s="1">
+        <f>K82-L82</f>
+        <v>1848</v>
+      </c>
+      <c r="N82" s="5">
+        <f>K82/F82</f>
+        <v>643.2439024390244</v>
+      </c>
+      <c r="O82" s="6">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="P82" s="6">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="Q82" s="7">
+        <v>0.313</v>
       </c>
     </row>
     <row r="83" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4538,44 +4583,47 @@
       <c r="D83" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N83" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O83" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P83" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q83" s="7" t="s">
-        <v>18</v>
+      <c r="E83" s="3">
+        <v>4</v>
+      </c>
+      <c r="F83" s="1">
+        <v>43</v>
+      </c>
+      <c r="G83" s="1">
+        <v>25</v>
+      </c>
+      <c r="H83" s="1">
+        <v>54</v>
+      </c>
+      <c r="I83" s="1">
+        <v>39</v>
+      </c>
+      <c r="J83" s="4">
+        <f>(G83+H83)/I83</f>
+        <v>2.0256410256410255</v>
+      </c>
+      <c r="K83" s="1">
+        <v>25680</v>
+      </c>
+      <c r="L83" s="1">
+        <v>22882</v>
+      </c>
+      <c r="M83" s="1">
+        <f>K83-L83</f>
+        <v>2798</v>
+      </c>
+      <c r="N83" s="5">
+        <f>K83/F83</f>
+        <v>597.20930232558135</v>
+      </c>
+      <c r="O83" s="6">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="P83" s="6">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="Q83" s="7">
+        <v>0.27800000000000002</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4585,44 +4633,47 @@
       <c r="D84" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N84" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q84" s="7" t="s">
-        <v>18</v>
+      <c r="E84" s="3">
+        <v>7</v>
+      </c>
+      <c r="F84" s="1">
+        <v>41</v>
+      </c>
+      <c r="G84" s="1">
+        <v>38</v>
+      </c>
+      <c r="H84" s="1">
+        <v>43</v>
+      </c>
+      <c r="I84" s="1">
+        <v>41</v>
+      </c>
+      <c r="J84" s="4">
+        <f>(G84+H84)/I84</f>
+        <v>1.975609756097561</v>
+      </c>
+      <c r="K84" s="1">
+        <v>23064</v>
+      </c>
+      <c r="L84" s="1">
+        <v>23183</v>
+      </c>
+      <c r="M84" s="1">
+        <f>K84-L84</f>
+        <v>-119</v>
+      </c>
+      <c r="N84" s="5">
+        <f>K84/F84</f>
+        <v>562.53658536585363</v>
+      </c>
+      <c r="O84" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="P84" s="6">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="Q84" s="7">
+        <v>0.154</v>
       </c>
     </row>
     <row r="85" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4632,44 +4683,47 @@
       <c r="D85" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E85" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N85" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q85" s="7" t="s">
-        <v>18</v>
+      <c r="E85" s="3">
+        <v>5</v>
+      </c>
+      <c r="F85" s="1">
+        <v>43</v>
+      </c>
+      <c r="G85" s="1">
+        <v>60</v>
+      </c>
+      <c r="H85" s="1">
+        <v>71</v>
+      </c>
+      <c r="I85" s="1">
+        <v>44</v>
+      </c>
+      <c r="J85" s="4">
+        <f>(G85+H85)/I85</f>
+        <v>2.9772727272727271</v>
+      </c>
+      <c r="K85" s="1">
+        <v>29149</v>
+      </c>
+      <c r="L85" s="1">
+        <v>23032</v>
+      </c>
+      <c r="M85" s="1">
+        <f>K85-L85</f>
+        <v>6117</v>
+      </c>
+      <c r="N85" s="5">
+        <f>K85/F85</f>
+        <v>677.88372093023258</v>
+      </c>
+      <c r="O85" s="6">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="P85" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Q85" s="7">
+        <v>0.3</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4679,44 +4733,47 @@
       <c r="D86" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N86" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q86" s="7" t="s">
-        <v>18</v>
+      <c r="E86" s="3">
+        <v>10</v>
+      </c>
+      <c r="F86" s="1">
+        <v>24</v>
+      </c>
+      <c r="G86" s="1">
+        <v>15</v>
+      </c>
+      <c r="H86" s="1">
+        <v>18</v>
+      </c>
+      <c r="I86" s="1">
+        <v>25</v>
+      </c>
+      <c r="J86" s="4">
+        <f>(G86+H86)/I86</f>
+        <v>1.32</v>
+      </c>
+      <c r="K86" s="1">
+        <v>10913</v>
+      </c>
+      <c r="L86" s="1">
+        <v>12933</v>
+      </c>
+      <c r="M86" s="1">
+        <f>K86-L86</f>
+        <v>-2020</v>
+      </c>
+      <c r="N86" s="5">
+        <f>K86/F86</f>
+        <v>454.70833333333331</v>
+      </c>
+      <c r="O86" s="6">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="P86" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Q86" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4774,46 +4831,46 @@
         <v>23</v>
       </c>
       <c r="E88" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F88" s="1">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G88" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H88" s="1">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I88" s="1">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J88" s="4">
         <f>(G88+H88)/I88</f>
-        <v>2.1363636363636362</v>
+        <v>1.2325581395348837</v>
       </c>
       <c r="K88" s="1">
-        <v>9823</v>
+        <v>15126</v>
       </c>
       <c r="L88" s="1">
-        <v>8989</v>
+        <v>15425</v>
       </c>
       <c r="M88" s="1">
         <f>K88-L88</f>
-        <v>834</v>
+        <v>-299</v>
       </c>
       <c r="N88" s="5">
         <f>K88/F88</f>
-        <v>427.08695652173913</v>
+        <v>368.92682926829269</v>
       </c>
       <c r="O88" s="6">
-        <v>0.435</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="P88" s="6">
-        <v>0.4</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="Q88" s="7">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4867,7 +4924,7 @@
     </row>
     <row r="90" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
@@ -5157,46 +5214,46 @@
         <v>23</v>
       </c>
       <c r="E96" s="3">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G96" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H96" s="1">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="I96" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J96" s="4">
         <f>(G96+H96)/I96</f>
-        <v>1.1200000000000001</v>
+        <v>2.1363636363636362</v>
       </c>
       <c r="K96" s="1">
-        <v>8113</v>
+        <v>9823</v>
       </c>
       <c r="L96" s="1">
-        <v>10306</v>
+        <v>8989</v>
       </c>
       <c r="M96" s="1">
         <f>K96-L96</f>
-        <v>-2193</v>
+        <v>834</v>
       </c>
       <c r="N96" s="5">
         <f>K96/F96</f>
-        <v>338.04166666666669</v>
+        <v>427.08695652173913</v>
       </c>
       <c r="O96" s="6">
-        <v>0.41699999999999998</v>
+        <v>0.435</v>
       </c>
       <c r="P96" s="6">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q96" s="7">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="97" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5250,54 +5307,51 @@
     </row>
     <row r="98" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E98" s="3">
-        <v>18</v>
-      </c>
-      <c r="F98" s="1">
-        <v>46</v>
-      </c>
-      <c r="G98" s="1">
-        <v>37</v>
-      </c>
-      <c r="H98" s="1">
-        <v>38</v>
-      </c>
-      <c r="I98" s="1">
-        <v>47</v>
-      </c>
-      <c r="J98" s="4">
-        <f t="shared" ref="J98:J104" si="3">(G98+H98)/I98</f>
-        <v>1.5957446808510638</v>
-      </c>
-      <c r="K98" s="1">
-        <v>30182</v>
-      </c>
-      <c r="L98" s="1">
-        <v>27797</v>
-      </c>
-      <c r="M98" s="1">
-        <f t="shared" ref="M98:M104" si="4">K98-L98</f>
-        <v>2385</v>
-      </c>
-      <c r="N98" s="5">
-        <f t="shared" ref="N98:N104" si="5">K98/F98</f>
-        <v>656.13043478260875</v>
-      </c>
-      <c r="O98" s="6">
-        <v>0.58699999999999997</v>
-      </c>
-      <c r="P98" s="6">
-        <v>0.48099999999999998</v>
-      </c>
-      <c r="Q98" s="7">
-        <v>7.6999999999999999E-2</v>
+      <c r="E98" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N98" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q98" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5307,47 +5361,44 @@
       <c r="D99" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E99" s="3">
-        <v>16</v>
-      </c>
-      <c r="F99" s="1">
-        <v>46</v>
-      </c>
-      <c r="G99" s="1">
-        <v>33</v>
-      </c>
-      <c r="H99" s="1">
-        <v>43</v>
-      </c>
-      <c r="I99" s="1">
-        <v>46</v>
-      </c>
-      <c r="J99" s="4">
-        <f t="shared" si="3"/>
-        <v>1.6521739130434783</v>
-      </c>
-      <c r="K99" s="1">
-        <v>24099</v>
-      </c>
-      <c r="L99" s="1">
-        <v>24712</v>
-      </c>
-      <c r="M99" s="1">
-        <f t="shared" si="4"/>
-        <v>-613</v>
-      </c>
-      <c r="N99" s="5">
-        <f t="shared" si="5"/>
-        <v>523.89130434782612</v>
-      </c>
-      <c r="O99" s="6">
-        <v>0.58699999999999997</v>
-      </c>
-      <c r="P99" s="6">
-        <v>0.51900000000000002</v>
-      </c>
-      <c r="Q99" s="7">
-        <v>7.0999999999999994E-2</v>
+      <c r="E99" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N99" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q99" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5357,47 +5408,44 @@
       <c r="D100" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E100" s="3">
-        <v>11</v>
-      </c>
-      <c r="F100" s="1">
-        <v>46</v>
-      </c>
-      <c r="G100" s="1">
-        <v>50</v>
-      </c>
-      <c r="H100" s="1">
-        <v>62</v>
-      </c>
-      <c r="I100" s="1">
-        <v>44</v>
-      </c>
-      <c r="J100" s="4">
-        <f t="shared" si="3"/>
-        <v>2.5454545454545454</v>
-      </c>
-      <c r="K100" s="1">
-        <v>28211</v>
-      </c>
-      <c r="L100" s="1">
-        <v>27318</v>
-      </c>
-      <c r="M100" s="1">
-        <f t="shared" si="4"/>
-        <v>893</v>
-      </c>
-      <c r="N100" s="5">
-        <f t="shared" si="5"/>
-        <v>613.28260869565213</v>
-      </c>
-      <c r="O100" s="6">
-        <v>0.45700000000000002</v>
-      </c>
-      <c r="P100" s="6">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="Q100" s="7">
-        <v>0.3</v>
+      <c r="E100" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N100" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q100" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5407,47 +5455,44 @@
       <c r="D101" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E101" s="3">
-        <v>10</v>
-      </c>
-      <c r="F101" s="1">
-        <v>46</v>
-      </c>
-      <c r="G101" s="1">
-        <v>39</v>
-      </c>
-      <c r="H101" s="1">
-        <v>60</v>
-      </c>
-      <c r="I101" s="1">
-        <v>45</v>
-      </c>
-      <c r="J101" s="4">
-        <f t="shared" si="3"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="K101" s="1">
-        <v>29027</v>
-      </c>
-      <c r="L101" s="1">
-        <v>31377</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" si="4"/>
-        <v>-2350</v>
-      </c>
-      <c r="N101" s="5">
-        <f t="shared" si="5"/>
-        <v>631.02173913043475</v>
-      </c>
-      <c r="O101" s="6">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="P101" s="6">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="Q101" s="7">
-        <v>0.2</v>
+      <c r="E101" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N101" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O101" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q101" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5457,47 +5502,44 @@
       <c r="D102" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E102" s="3">
-        <v>19</v>
-      </c>
-      <c r="F102" s="1">
-        <v>46</v>
-      </c>
-      <c r="G102" s="1">
-        <v>26</v>
-      </c>
-      <c r="H102" s="1">
-        <v>45</v>
-      </c>
-      <c r="I102" s="1">
-        <v>45</v>
-      </c>
-      <c r="J102" s="4">
-        <f t="shared" si="3"/>
-        <v>1.5777777777777777</v>
-      </c>
-      <c r="K102" s="1">
-        <v>21915</v>
-      </c>
-      <c r="L102" s="1">
-        <v>23180</v>
-      </c>
-      <c r="M102" s="1">
-        <f t="shared" si="4"/>
-        <v>-1265</v>
-      </c>
-      <c r="N102" s="5">
-        <f t="shared" si="5"/>
-        <v>476.41304347826087</v>
-      </c>
-      <c r="O102" s="6">
-        <v>0.45700000000000002</v>
-      </c>
-      <c r="P102" s="6">
-        <v>0.52400000000000002</v>
-      </c>
-      <c r="Q102" s="7">
-        <v>9.0999999999999998E-2</v>
+      <c r="E102" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N102" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q102" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5507,47 +5549,44 @@
       <c r="D103" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E103" s="3">
-        <v>12</v>
-      </c>
-      <c r="F103" s="1">
-        <v>46</v>
-      </c>
-      <c r="G103" s="1">
-        <v>46</v>
-      </c>
-      <c r="H103" s="1">
-        <v>52</v>
-      </c>
-      <c r="I103" s="1">
-        <v>45</v>
-      </c>
-      <c r="J103" s="4">
-        <f t="shared" si="3"/>
-        <v>2.1777777777777776</v>
-      </c>
-      <c r="K103" s="1">
-        <v>23165</v>
-      </c>
-      <c r="L103" s="1">
-        <v>26004</v>
-      </c>
-      <c r="M103" s="1">
-        <f t="shared" si="4"/>
-        <v>-2839</v>
-      </c>
-      <c r="N103" s="5">
-        <f t="shared" si="5"/>
-        <v>503.58695652173913</v>
-      </c>
-      <c r="O103" s="6">
-        <v>0.435</v>
-      </c>
-      <c r="P103" s="6">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q103" s="7">
-        <v>0.36399999999999999</v>
+      <c r="E103" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N103" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q103" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5558,46 +5597,46 @@
         <v>23</v>
       </c>
       <c r="E104" s="3">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F104" s="1">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G104" s="1">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H104" s="1">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="I104" s="1">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="J104" s="4">
-        <f t="shared" si="3"/>
-        <v>2.5555555555555554</v>
+        <f>(G104+H104)/I104</f>
+        <v>1.1200000000000001</v>
       </c>
       <c r="K104" s="1">
-        <v>23112</v>
+        <v>8113</v>
       </c>
       <c r="L104" s="1">
-        <v>21274</v>
+        <v>10306</v>
       </c>
       <c r="M104" s="1">
-        <f t="shared" si="4"/>
-        <v>1838</v>
+        <f>K104-L104</f>
+        <v>-2193</v>
       </c>
       <c r="N104" s="5">
-        <f t="shared" si="5"/>
-        <v>502.43478260869563</v>
+        <f>K104/F104</f>
+        <v>338.04166666666669</v>
       </c>
       <c r="O104" s="6">
-        <v>0.58699999999999997</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="P104" s="6">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
       <c r="Q104" s="7">
-        <v>0.11799999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5651,51 +5690,54 @@
     </row>
     <row r="106" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J106" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N106" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q106" s="7" t="s">
-        <v>18</v>
+      <c r="E106" s="3">
+        <v>18</v>
+      </c>
+      <c r="F106" s="1">
+        <v>46</v>
+      </c>
+      <c r="G106" s="1">
+        <v>37</v>
+      </c>
+      <c r="H106" s="1">
+        <v>38</v>
+      </c>
+      <c r="I106" s="1">
+        <v>47</v>
+      </c>
+      <c r="J106" s="4">
+        <f t="shared" ref="J106:J112" si="3">(G106+H106)/I106</f>
+        <v>1.5957446808510638</v>
+      </c>
+      <c r="K106" s="1">
+        <v>30182</v>
+      </c>
+      <c r="L106" s="1">
+        <v>27797</v>
+      </c>
+      <c r="M106" s="1">
+        <f t="shared" ref="M106:M112" si="4">K106-L106</f>
+        <v>2385</v>
+      </c>
+      <c r="N106" s="5">
+        <f t="shared" ref="N106:N112" si="5">K106/F106</f>
+        <v>656.13043478260875</v>
+      </c>
+      <c r="O106" s="6">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="P106" s="6">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="Q106" s="7">
+        <v>7.6999999999999999E-2</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5705,44 +5747,47 @@
       <c r="D107" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L107" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M107" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N107" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O107" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q107" s="7" t="s">
-        <v>18</v>
+      <c r="E107" s="3">
+        <v>16</v>
+      </c>
+      <c r="F107" s="1">
+        <v>46</v>
+      </c>
+      <c r="G107" s="1">
+        <v>33</v>
+      </c>
+      <c r="H107" s="1">
+        <v>43</v>
+      </c>
+      <c r="I107" s="1">
+        <v>46</v>
+      </c>
+      <c r="J107" s="4">
+        <f t="shared" si="3"/>
+        <v>1.6521739130434783</v>
+      </c>
+      <c r="K107" s="1">
+        <v>24099</v>
+      </c>
+      <c r="L107" s="1">
+        <v>24712</v>
+      </c>
+      <c r="M107" s="1">
+        <f t="shared" si="4"/>
+        <v>-613</v>
+      </c>
+      <c r="N107" s="5">
+        <f t="shared" si="5"/>
+        <v>523.89130434782612</v>
+      </c>
+      <c r="O107" s="6">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="P107" s="6">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="Q107" s="7">
+        <v>7.0999999999999994E-2</v>
       </c>
     </row>
     <row r="108" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5753,46 +5798,46 @@
         <v>19</v>
       </c>
       <c r="E108" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G108" s="1">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H108" s="1">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="I108" s="1">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J108" s="4">
-        <f>(G108+H108)/I108</f>
-        <v>3.3793103448275863</v>
+        <f t="shared" si="3"/>
+        <v>2.5454545454545454</v>
       </c>
       <c r="K108" s="1">
-        <v>21561</v>
+        <v>28211</v>
       </c>
       <c r="L108" s="1">
-        <v>18200</v>
+        <v>27318</v>
       </c>
       <c r="M108" s="1">
-        <f>K108-L108</f>
-        <v>3361</v>
+        <f t="shared" si="4"/>
+        <v>893</v>
       </c>
       <c r="N108" s="5">
-        <f>K108/F108</f>
-        <v>634.14705882352939</v>
+        <f t="shared" si="5"/>
+        <v>613.28260869565213</v>
       </c>
       <c r="O108" s="6">
-        <v>0.61799999999999999</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="P108" s="6">
-        <v>0.57099999999999995</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="Q108" s="7">
-        <v>0.41699999999999998</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="109" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5802,44 +5847,47 @@
       <c r="D109" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E109" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M109" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N109" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O109" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q109" s="7" t="s">
-        <v>18</v>
+      <c r="E109" s="3">
+        <v>10</v>
+      </c>
+      <c r="F109" s="1">
+        <v>46</v>
+      </c>
+      <c r="G109" s="1">
+        <v>39</v>
+      </c>
+      <c r="H109" s="1">
+        <v>60</v>
+      </c>
+      <c r="I109" s="1">
+        <v>45</v>
+      </c>
+      <c r="J109" s="4">
+        <f t="shared" si="3"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K109" s="1">
+        <v>29027</v>
+      </c>
+      <c r="L109" s="1">
+        <v>31377</v>
+      </c>
+      <c r="M109" s="1">
+        <f t="shared" si="4"/>
+        <v>-2350</v>
+      </c>
+      <c r="N109" s="5">
+        <f t="shared" si="5"/>
+        <v>631.02173913043475</v>
+      </c>
+      <c r="O109" s="6">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="P109" s="6">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="Q109" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="110" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5849,44 +5897,47 @@
       <c r="D110" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E110" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M110" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N110" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q110" s="7" t="s">
-        <v>18</v>
+      <c r="E110" s="3">
+        <v>19</v>
+      </c>
+      <c r="F110" s="1">
+        <v>46</v>
+      </c>
+      <c r="G110" s="1">
+        <v>26</v>
+      </c>
+      <c r="H110" s="1">
+        <v>45</v>
+      </c>
+      <c r="I110" s="1">
+        <v>45</v>
+      </c>
+      <c r="J110" s="4">
+        <f t="shared" si="3"/>
+        <v>1.5777777777777777</v>
+      </c>
+      <c r="K110" s="1">
+        <v>21915</v>
+      </c>
+      <c r="L110" s="1">
+        <v>23180</v>
+      </c>
+      <c r="M110" s="1">
+        <f t="shared" si="4"/>
+        <v>-1265</v>
+      </c>
+      <c r="N110" s="5">
+        <f t="shared" si="5"/>
+        <v>476.41304347826087</v>
+      </c>
+      <c r="O110" s="6">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="P110" s="6">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="Q110" s="7">
+        <v>9.0999999999999998E-2</v>
       </c>
     </row>
     <row r="111" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5896,44 +5947,47 @@
       <c r="D111" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N111" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O111" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q111" s="7" t="s">
-        <v>18</v>
+      <c r="E111" s="3">
+        <v>12</v>
+      </c>
+      <c r="F111" s="1">
+        <v>46</v>
+      </c>
+      <c r="G111" s="1">
+        <v>46</v>
+      </c>
+      <c r="H111" s="1">
+        <v>52</v>
+      </c>
+      <c r="I111" s="1">
+        <v>45</v>
+      </c>
+      <c r="J111" s="4">
+        <f t="shared" si="3"/>
+        <v>2.1777777777777776</v>
+      </c>
+      <c r="K111" s="1">
+        <v>23165</v>
+      </c>
+      <c r="L111" s="1">
+        <v>26004</v>
+      </c>
+      <c r="M111" s="1">
+        <f t="shared" si="4"/>
+        <v>-2839</v>
+      </c>
+      <c r="N111" s="5">
+        <f t="shared" si="5"/>
+        <v>503.58695652173913</v>
+      </c>
+      <c r="O111" s="6">
+        <v>0.435</v>
+      </c>
+      <c r="P111" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Q111" s="7">
+        <v>0.36399999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -5944,46 +5998,46 @@
         <v>23</v>
       </c>
       <c r="E112" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G112" s="1">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H112" s="1">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I112" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J112" s="4">
-        <f>(G112+H112)/I112</f>
-        <v>1.5116279069767442</v>
+        <f t="shared" si="3"/>
+        <v>2.5555555555555554</v>
       </c>
       <c r="K112" s="1">
-        <v>13138</v>
+        <v>23112</v>
       </c>
       <c r="L112" s="1">
-        <v>16312</v>
+        <v>21274</v>
       </c>
       <c r="M112" s="1">
-        <f>K112-L112</f>
-        <v>-3174</v>
+        <f t="shared" si="4"/>
+        <v>1838</v>
       </c>
       <c r="N112" s="5">
-        <f>K112/F112</f>
-        <v>312.8095238095238</v>
+        <f t="shared" si="5"/>
+        <v>502.43478260869563</v>
       </c>
       <c r="O112" s="6">
-        <v>0.45200000000000001</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="P112" s="6">
-        <v>0.26300000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="Q112" s="7">
-        <v>0</v>
+        <v>0.11799999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -6037,7 +6091,7 @@
     </row>
     <row r="114" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -6139,46 +6193,46 @@
         <v>19</v>
       </c>
       <c r="E116" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F116" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G116" s="1">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H116" s="1">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I116" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J116" s="4">
         <f>(G116+H116)/I116</f>
-        <v>1.9666666666666666</v>
+        <v>3.3793103448275863</v>
       </c>
       <c r="K116" s="1">
-        <v>13694</v>
+        <v>21561</v>
       </c>
       <c r="L116" s="1">
-        <v>16248</v>
+        <v>18200</v>
       </c>
       <c r="M116" s="1">
         <f>K116-L116</f>
-        <v>-2554</v>
+        <v>3361</v>
       </c>
       <c r="N116" s="5">
         <f>K116/F116</f>
-        <v>456.46666666666664</v>
+        <v>634.14705882352939</v>
       </c>
       <c r="O116" s="6">
-        <v>0.433</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="P116" s="6">
-        <v>0.308</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="Q116" s="7">
-        <v>0.25</v>
+        <v>0.41699999999999998</v>
       </c>
     </row>
     <row r="117" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -6330,49 +6384,49 @@
         <v>23</v>
       </c>
       <c r="E120" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G120" s="1">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H120" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I120" s="1">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J120" s="4">
         <f>(G120+H120)/I120</f>
-        <v>1.1599999999999999</v>
+        <v>1.5116279069767442</v>
       </c>
       <c r="K120" s="1">
-        <v>7497</v>
+        <v>13138</v>
       </c>
       <c r="L120" s="1">
-        <v>11106</v>
+        <v>16312</v>
       </c>
       <c r="M120" s="1">
         <f>K120-L120</f>
-        <v>-3609</v>
+        <v>-3174</v>
       </c>
       <c r="N120" s="5">
         <f>K120/F120</f>
-        <v>312.375</v>
+        <v>312.8095238095238</v>
       </c>
       <c r="O120" s="6">
-        <v>0.625</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="P120" s="6">
-        <v>0.4</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="Q120" s="7">
-        <v>0.16700000000000001</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>0</v>
       </c>
@@ -6421,109 +6475,103 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
       <c r="D122" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E122" s="3">
-        <v>30</v>
-      </c>
-      <c r="F122" s="1">
-        <v>17</v>
-      </c>
-      <c r="G122" s="1">
-        <v>20</v>
-      </c>
-      <c r="H122" s="1">
-        <v>11</v>
-      </c>
-      <c r="I122" s="1">
-        <v>18</v>
-      </c>
-      <c r="J122" s="4">
-        <f>(G122+H122)/I122</f>
-        <v>1.7222222222222223</v>
-      </c>
-      <c r="K122" s="1">
-        <v>7086</v>
-      </c>
-      <c r="L122" s="1">
-        <v>7170</v>
-      </c>
-      <c r="M122" s="1">
-        <f>K122-L122</f>
-        <v>-84</v>
-      </c>
-      <c r="N122" s="5">
-        <f>K122/F122</f>
-        <v>416.8235294117647</v>
-      </c>
-      <c r="O122" s="6">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="P122" s="6">
-        <v>0.28599999999999998</v>
-      </c>
-      <c r="Q122" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E122" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N122" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P122" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q122" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
       <c r="D123" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E123" s="3">
-        <v>22</v>
-      </c>
-      <c r="F123" s="1">
-        <v>36</v>
-      </c>
-      <c r="G123" s="1">
-        <v>22</v>
-      </c>
-      <c r="H123" s="1">
-        <v>35</v>
-      </c>
-      <c r="I123" s="1">
-        <v>35</v>
-      </c>
-      <c r="J123" s="4">
-        <f>(G123+H123)/I123</f>
-        <v>1.6285714285714286</v>
-      </c>
-      <c r="K123" s="1">
-        <v>14824</v>
-      </c>
-      <c r="L123" s="1">
-        <v>14466</v>
-      </c>
-      <c r="M123" s="1">
-        <f>K123-L123</f>
-        <v>358</v>
-      </c>
-      <c r="N123" s="5">
-        <f>K123/F123</f>
-        <v>411.77777777777777</v>
-      </c>
-      <c r="O123" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="P123" s="6">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="Q123" s="7">
-        <v>0.14299999999999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E123" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N123" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O123" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P123" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q123" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
@@ -6531,99 +6579,96 @@
         <v>19</v>
       </c>
       <c r="E124" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F124" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G124" s="1">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H124" s="1">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="I124" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J124" s="4">
         <f>(G124+H124)/I124</f>
-        <v>2.7894736842105261</v>
+        <v>1.9666666666666666</v>
       </c>
       <c r="K124" s="1">
-        <v>23749</v>
+        <v>13694</v>
       </c>
       <c r="L124" s="1">
-        <v>20933</v>
+        <v>16248</v>
       </c>
       <c r="M124" s="1">
         <f>K124-L124</f>
-        <v>2816</v>
+        <v>-2554</v>
       </c>
       <c r="N124" s="5">
         <f>K124/F124</f>
-        <v>565.45238095238096</v>
+        <v>456.46666666666664</v>
       </c>
       <c r="O124" s="6">
-        <v>0.66700000000000004</v>
+        <v>0.433</v>
       </c>
       <c r="P124" s="6">
-        <v>0.57099999999999995</v>
+        <v>0.308</v>
       </c>
       <c r="Q124" s="7">
-        <v>0.313</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
       <c r="D125" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E125" s="3">
-        <v>16</v>
-      </c>
-      <c r="F125" s="1">
-        <v>42</v>
-      </c>
-      <c r="G125" s="1">
-        <v>30</v>
-      </c>
-      <c r="H125" s="1">
-        <v>50</v>
-      </c>
-      <c r="I125" s="1">
-        <v>42</v>
-      </c>
-      <c r="J125" s="4">
-        <f>(G125+H125)/I125</f>
-        <v>1.9047619047619047</v>
-      </c>
-      <c r="K125" s="1">
-        <v>26822</v>
-      </c>
-      <c r="L125" s="1">
-        <v>24993</v>
-      </c>
-      <c r="M125" s="1">
-        <f>K125-L125</f>
-        <v>1829</v>
-      </c>
-      <c r="N125" s="5">
-        <f>K125/F125</f>
-        <v>638.61904761904759</v>
-      </c>
-      <c r="O125" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="P125" s="6">
-        <v>0.23799999999999999</v>
-      </c>
-      <c r="Q125" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E125" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M125" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N125" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O125" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P125" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q125" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -6670,57 +6715,54 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
       <c r="D127" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E127" s="3">
-        <v>8</v>
-      </c>
-      <c r="F127" s="1">
-        <v>42</v>
-      </c>
-      <c r="G127" s="1">
-        <v>65</v>
-      </c>
-      <c r="H127" s="1">
-        <v>60</v>
-      </c>
-      <c r="I127" s="1">
-        <v>39</v>
-      </c>
-      <c r="J127" s="4">
-        <f>(G127+H127)/I127</f>
-        <v>3.2051282051282053</v>
-      </c>
-      <c r="K127" s="1">
-        <v>30807</v>
-      </c>
-      <c r="L127" s="1">
-        <v>20825</v>
-      </c>
-      <c r="M127" s="1">
-        <f>K127-L127</f>
-        <v>9982</v>
-      </c>
-      <c r="N127" s="5">
-        <f>K127/F127</f>
-        <v>733.5</v>
-      </c>
-      <c r="O127" s="6">
-        <v>0.64300000000000002</v>
-      </c>
-      <c r="P127" s="6">
-        <v>0.48099999999999998</v>
-      </c>
-      <c r="Q127" s="7">
-        <v>0.23100000000000001</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E127" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N127" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O127" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P127" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q127" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
@@ -6728,82 +6770,482 @@
         <v>23</v>
       </c>
       <c r="E128" s="3">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F128" s="1">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G128" s="1">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H128" s="1">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="I128" s="1">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="J128" s="4">
         <f>(G128+H128)/I128</f>
-        <v>2.3333333333333335</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="K128" s="1">
-        <v>24658</v>
+        <v>7497</v>
       </c>
       <c r="L128" s="1">
-        <v>19681</v>
+        <v>11106</v>
       </c>
       <c r="M128" s="1">
         <f>K128-L128</f>
-        <v>4977</v>
+        <v>-3609</v>
       </c>
       <c r="N128" s="5">
         <f>K128/F128</f>
+        <v>312.375</v>
+      </c>
+      <c r="O128" s="6">
+        <v>0.625</v>
+      </c>
+      <c r="P128" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="Q128" s="7">
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q129" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" s="3">
+        <v>30</v>
+      </c>
+      <c r="F130" s="1">
+        <v>17</v>
+      </c>
+      <c r="G130" s="1">
+        <v>20</v>
+      </c>
+      <c r="H130" s="1">
+        <v>11</v>
+      </c>
+      <c r="I130" s="1">
+        <v>18</v>
+      </c>
+      <c r="J130" s="4">
+        <f>(G130+H130)/I130</f>
+        <v>1.7222222222222223</v>
+      </c>
+      <c r="K130" s="1">
+        <v>7086</v>
+      </c>
+      <c r="L130" s="1">
+        <v>7170</v>
+      </c>
+      <c r="M130" s="1">
+        <f>K130-L130</f>
+        <v>-84</v>
+      </c>
+      <c r="N130" s="5">
+        <f>K130/F130</f>
+        <v>416.8235294117647</v>
+      </c>
+      <c r="O130" s="6">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="P130" s="6">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="Q130" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="9"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" s="3">
+        <v>22</v>
+      </c>
+      <c r="F131" s="1">
+        <v>36</v>
+      </c>
+      <c r="G131" s="1">
+        <v>22</v>
+      </c>
+      <c r="H131" s="1">
+        <v>35</v>
+      </c>
+      <c r="I131" s="1">
+        <v>35</v>
+      </c>
+      <c r="J131" s="4">
+        <f>(G131+H131)/I131</f>
+        <v>1.6285714285714286</v>
+      </c>
+      <c r="K131" s="1">
+        <v>14824</v>
+      </c>
+      <c r="L131" s="1">
+        <v>14466</v>
+      </c>
+      <c r="M131" s="1">
+        <f>K131-L131</f>
+        <v>358</v>
+      </c>
+      <c r="N131" s="5">
+        <f>K131/F131</f>
+        <v>411.77777777777777</v>
+      </c>
+      <c r="O131" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="P131" s="6">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="Q131" s="7">
+        <v>0.14299999999999999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="9"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="3">
+        <v>4</v>
+      </c>
+      <c r="F132" s="1">
+        <v>42</v>
+      </c>
+      <c r="G132" s="1">
+        <v>41</v>
+      </c>
+      <c r="H132" s="1">
+        <v>65</v>
+      </c>
+      <c r="I132" s="1">
+        <v>38</v>
+      </c>
+      <c r="J132" s="4">
+        <f>(G132+H132)/I132</f>
+        <v>2.7894736842105261</v>
+      </c>
+      <c r="K132" s="1">
+        <v>23749</v>
+      </c>
+      <c r="L132" s="1">
+        <v>20933</v>
+      </c>
+      <c r="M132" s="1">
+        <f>K132-L132</f>
+        <v>2816</v>
+      </c>
+      <c r="N132" s="5">
+        <f>K132/F132</f>
+        <v>565.45238095238096</v>
+      </c>
+      <c r="O132" s="6">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P132" s="6">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="Q132" s="7">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E133" s="3">
+        <v>16</v>
+      </c>
+      <c r="F133" s="1">
+        <v>42</v>
+      </c>
+      <c r="G133" s="1">
+        <v>30</v>
+      </c>
+      <c r="H133" s="1">
+        <v>50</v>
+      </c>
+      <c r="I133" s="1">
+        <v>42</v>
+      </c>
+      <c r="J133" s="4">
+        <f>(G133+H133)/I133</f>
+        <v>1.9047619047619047</v>
+      </c>
+      <c r="K133" s="1">
+        <v>26822</v>
+      </c>
+      <c r="L133" s="1">
+        <v>24993</v>
+      </c>
+      <c r="M133" s="1">
+        <f>K133-L133</f>
+        <v>1829</v>
+      </c>
+      <c r="N133" s="5">
+        <f>K133/F133</f>
+        <v>638.61904761904759</v>
+      </c>
+      <c r="O133" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="P133" s="6">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="Q133" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="9"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N134" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O134" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P134" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q134" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="9"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E135" s="3">
+        <v>8</v>
+      </c>
+      <c r="F135" s="1">
+        <v>42</v>
+      </c>
+      <c r="G135" s="1">
+        <v>65</v>
+      </c>
+      <c r="H135" s="1">
+        <v>60</v>
+      </c>
+      <c r="I135" s="1">
+        <v>39</v>
+      </c>
+      <c r="J135" s="4">
+        <f>(G135+H135)/I135</f>
+        <v>3.2051282051282053</v>
+      </c>
+      <c r="K135" s="1">
+        <v>30807</v>
+      </c>
+      <c r="L135" s="1">
+        <v>20825</v>
+      </c>
+      <c r="M135" s="1">
+        <f>K135-L135</f>
+        <v>9982</v>
+      </c>
+      <c r="N135" s="5">
+        <f>K135/F135</f>
+        <v>733.5</v>
+      </c>
+      <c r="O135" s="6">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="P135" s="6">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="Q135" s="7">
+        <v>0.23100000000000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="9"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136" s="3">
+        <v>5</v>
+      </c>
+      <c r="F136" s="1">
+        <v>42</v>
+      </c>
+      <c r="G136" s="1">
+        <v>52</v>
+      </c>
+      <c r="H136" s="1">
+        <v>46</v>
+      </c>
+      <c r="I136" s="1">
+        <v>42</v>
+      </c>
+      <c r="J136" s="4">
+        <f>(G136+H136)/I136</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="K136" s="1">
+        <v>24658</v>
+      </c>
+      <c r="L136" s="1">
+        <v>19681</v>
+      </c>
+      <c r="M136" s="1">
+        <f>K136-L136</f>
+        <v>4977</v>
+      </c>
+      <c r="N136" s="5">
+        <f>K136/F136</f>
         <v>587.09523809523807</v>
       </c>
-      <c r="O128" s="6">
+      <c r="O136" s="6">
         <v>0.59499999999999997</v>
       </c>
-      <c r="P128" s="6">
+      <c r="P136" s="6">
         <v>0.48</v>
       </c>
-      <c r="Q128" s="7">
+      <c r="Q136" s="7">
         <v>0.25</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="34">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A58:C64"/>
-    <mergeCell ref="A34:C40"/>
-    <mergeCell ref="A114:C120"/>
-    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A2:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A66:C72"/>
+    <mergeCell ref="A42:C48"/>
     <mergeCell ref="A122:C128"/>
     <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A130:C136"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A18:C24"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A114:C120"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A129:C129"/>
     <mergeCell ref="A10:C16"/>
+    <mergeCell ref="A26:C32"/>
+    <mergeCell ref="A34:C40"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A50:C56"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A82:C88"/>
+    <mergeCell ref="A58:C64"/>
+    <mergeCell ref="A98:C104"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A106:C112"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A106:C112"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A2:C8"/>
-    <mergeCell ref="A18:C24"/>
-    <mergeCell ref="A26:C32"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A42:C48"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A90:C96"/>
     <mergeCell ref="A74:C80"/>
-    <mergeCell ref="A50:C56"/>
-    <mergeCell ref="A90:C96"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A98:C104"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A82:C88"/>
-    <mergeCell ref="A66:C72"/>
-    <mergeCell ref="A33:C33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
